--- a/Parallax_Portfolio_of_the_Week_2026-06-29.xlsx
+++ b/Parallax_Portfolio_of_the_Week_2026-06-29.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -466,12 +466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMD.O</t>
+          <t>MSFT.O</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,12 +481,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSFT.O</t>
+          <t>AAPL.O</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -496,12 +496,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AAPL.O</t>
+          <t>GOOGL.O</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -511,12 +511,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GOOGL.O</t>
+          <t>META.O</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -526,12 +526,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>META.O</t>
+          <t>AMZN.O</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,12 +541,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MU.O</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,12 +571,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMAT.O</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -586,12 +586,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LRCX.O</t>
+          <t>PANW.O</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -601,12 +601,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QCOM.O</t>
+          <t>ADBE.O</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -616,12 +616,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>AMD.O</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,12 +631,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASML.O</t>
+          <t>QCOM.O</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -646,7 +646,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -706,7 +706,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -721,12 +721,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -736,12 +736,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DHI</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -751,12 +751,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -766,12 +766,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -781,12 +781,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BLD</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -796,12 +796,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -811,12 +811,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -826,12 +826,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -841,12 +841,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="C29" t="n">
